--- a/artfynd/A 41346-2021 artfynd.xlsx
+++ b/artfynd/A 41346-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -784,6 +784,118 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>120422166</v>
+      </c>
+      <c r="B3" t="n">
+        <v>90356</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2015</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Vit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hydnum albidum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Peck</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Fallskogen, Gtl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>691577</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6361412</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Linnea Ingelsbo</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Linnea Ingelsbo</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 41346-2021 artfynd.xlsx
+++ b/artfynd/A 41346-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120421885</v>
+        <v>120422166</v>
       </c>
       <c r="B2" t="n">
-        <v>91879</v>
+        <v>90356</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5964</v>
+        <v>2015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120422166</v>
+        <v>120421885</v>
       </c>
       <c r="B3" t="n">
-        <v>90356</v>
+        <v>91879</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2015</v>
+        <v>5964</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Peck</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD3" t="b">
